--- a/01_analyses_states/West Bengal/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/West Bengal/results/SoIB_summaries.xlsx
@@ -509,7 +509,7 @@
         <v>7</v>
       </c>
       <c r="E2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -520,10 +520,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>17.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -537,7 +537,7 @@
         <v>46</v>
       </c>
       <c r="E4">
-        <v>63</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -551,7 +551,7 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -565,7 +565,7 @@
         <v>4</v>
       </c>
       <c r="E6">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -573,10 +573,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C7">
-        <v>119</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -584,10 +584,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>643</v>
+        <v>675</v>
       </c>
       <c r="C8">
-        <v>493</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -682,7 +682,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -690,7 +690,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -698,7 +698,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -727,7 +727,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>685</v>
+        <v>693</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -735,7 +735,7 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>192</v>
+        <v>147</v>
       </c>
       <c r="C4">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -792,16 +792,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2">
-        <v>57.5</v>
+        <v>57.9</v>
       </c>
       <c r="D2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E2">
-        <v>70.90000000000001</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -812,13 +812,13 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>42.5</v>
+        <v>42.1</v>
       </c>
       <c r="D3">
         <v>25</v>
       </c>
       <c r="E3">
-        <v>29.1</v>
+        <v>28.7</v>
       </c>
     </row>
   </sheetData>
